--- a/data/trans_orig/Q5402-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44212</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257273</t>
+          <t>256426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275979</t>
+          <t>275452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313169</t>
+          <t>312821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>329937</t>
+          <t>329971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>575514</t>
+          <t>574619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601122</t>
+          <t>601789</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36833</t>
+          <t>37171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>65779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39176</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47991</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>47618</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>78825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149680</t>
+          <t>148291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172119</t>
+          <t>172814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253029</t>
+          <t>253233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>282776</t>
+          <t>281476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>410328</t>
+          <t>409603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>448569</t>
+          <t>449764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>48456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115365</t>
+          <t>114224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412889</t>
+          <t>413377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>443809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571453</t>
+          <t>572975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607620</t>
+          <t>608287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994367</t>
+          <t>994755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1041130</t>
+          <t>1043104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56334</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>263318</t>
+          <t>261459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285581</t>
+          <t>285981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311587</t>
+          <t>310494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333211</t>
+          <t>332511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>581641</t>
+          <t>580752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>614379</t>
+          <t>613610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57478</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>50653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82756</t>
+          <t>81578</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88383</t>
+          <t>89851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126096</t>
+          <t>128953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>42871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72626</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81504</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120797</t>
+          <t>120935</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146377</t>
+          <t>146256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179486</t>
+          <t>178376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247686</t>
+          <t>250187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285095</t>
+          <t>285448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>406827</t>
+          <t>404544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>456680</t>
+          <t>456287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41497</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60344</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95538</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109837</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156214</t>
+          <t>153213</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>59792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94463</t>
+          <t>92944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120702</t>
+          <t>119357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167168</t>
+          <t>164694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>417477</t>
+          <t>417026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459168</t>
+          <t>459388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564794</t>
+          <t>568970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612081</t>
+          <t>614563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>998660</t>
+          <t>997398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1062279</t>
+          <t>1057164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305516</t>
+          <t>304945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322541</t>
+          <t>323278</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>350642</t>
+          <t>351131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>367504</t>
+          <t>367661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>664003</t>
+          <t>664205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686629</t>
+          <t>686642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39426</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66294</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>60566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95341</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>47986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74773</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113374</t>
+          <t>114092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179239</t>
+          <t>178993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204460</t>
+          <t>205477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>273155</t>
+          <t>274641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316179</t>
+          <t>316133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>464777</t>
+          <t>464720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>513776</t>
+          <t>511431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68412</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>104438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55035</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93122</t>
+          <t>90620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141925</t>
+          <t>141303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>491916</t>
+          <t>491892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>522488</t>
+          <t>523857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631389</t>
+          <t>633775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>678434</t>
+          <t>678758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1134626</t>
+          <t>1138489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1193388</t>
+          <t>1192394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>51551</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64623</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>334880</t>
+          <t>371655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>326601</t>
+          <t>361810</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>343834</t>
+          <t>380222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>577505</t>
+          <t>404363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>557835</t>
+          <t>395024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>595898</t>
+          <t>412269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>912385</t>
+          <t>776019</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>889548</t>
+          <t>763700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>942580</t>
+          <t>787799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>975408</t>
+          <t>845004</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>975408</t>
+          <t>845004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>975408</t>
+          <t>845004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>74323</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81007</t>
+          <t>85662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>106831</t>
+          <t>113730</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92692</t>
+          <t>99854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122501</t>
+          <t>129302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42043</t>
+          <t>44215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53135</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79107</t>
+          <t>86280</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68254</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90299</t>
+          <t>97867</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>121150</t>
+          <t>130496</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>106556</t>
+          <t>115252</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135532</t>
+          <t>148700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>201161</t>
+          <t>224106</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187836</t>
+          <t>210827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211959</t>
+          <t>235554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>277238</t>
+          <t>304006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>263131</t>
+          <t>288093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290597</t>
+          <t>318752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>478400</t>
+          <t>528112</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462647</t>
+          <t>507256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>497123</t>
+          <t>548185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48633</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>41588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59650</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74999</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>92568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>123631</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80152</t>
+          <t>114706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>147471</t>
+          <t>149219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52417</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76764</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104047</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>102188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>167373</t>
+          <t>182047</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108064</t>
+          <t>163107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198804</t>
+          <t>205064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>536041</t>
+          <t>595762</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519871</t>
+          <t>577990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549743</t>
+          <t>610069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>854743</t>
+          <t>708369</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>801896</t>
+          <t>689630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>934419</t>
+          <t>724073</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1390784</t>
+          <t>1304131</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1342454</t>
+          <t>1276180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1498299</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
